--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -458,7 +458,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
   </cols>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>历史遗留</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>【遗留】关于Burn ISO选择win11镜像时，无法勾选跳过硬件检测的问题</t>
+          <t>关于关闭活动条后，图片变更不会再出触发活动条的问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24 15:26:28</t>
+          <t>2026-04-29 18:22:51</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>韦家鹏</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 16:01:03</t>
+          <t>2026-05-08 09:45:08</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 16:00:04</t>
+          <t>2026-05-08 09:43:02</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>bydesign</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>42410</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>关于断网情况下活动入口没有保持上一次状态问题</t>
+          <t>关于arm设备没有屏蔽bootable media入口问题</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -681,17 +681,13 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:14:15</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>韦家鹏</t>
-        </is>
-      </c>
+          <t>2026-05-07 10:30:01</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:51</t>
+          <t>2026-05-07 17:43:39</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -701,25 +697,29 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:16:10</t>
+          <t>2026-05-07 13:51:09</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-07 17:43:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>42256</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>信息收集</t>
+          <t>网络克隆</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>【信息收集】关于进入PE执行克隆时，克隆结果Result_Clone动作的属性收集错误的问题</t>
+          <t>【网络克隆】关于网络克隆许可扣减后，在关于中的可用数量不变的问题</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -754,27 +754,23 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>李俊杰</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 10:47:17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>杨光雪</t>
-        </is>
-      </c>
+          <t>2026-04-01 10:32:10</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 11:30:13</t>
+          <t>2026-05-08 10:10:16</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -784,7 +780,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28 11:29:40</t>
+          <t>2026-05-07 13:06:56</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -792,17 +788,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-08 10:10:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>42386</t>
+          <t>42322</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -817,22 +817,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>系统克隆</t>
+          <t>网络克隆</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>【系统克隆】关于离线系统克隆出错的问题</t>
+          <t>【网络克隆】关于server部署在公网服务器上时，显示下载client的地址为私有IP的问题</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -847,38 +847,370 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24 11:08:37</t>
+          <t>2026-04-14 14:15:10</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>韦家鹏</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27 11:19:32</t>
+          <t>2026-05-07 10:41:27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>郑浪</t>
+          <t>贺照云</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-27 11:16:26</t>
+          <t>2026-05-07 10:40:53</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>postponed</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>42407</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>系统克隆</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>【系统克隆】关于GPT系统克隆后，未修改BCD的问题（老问题）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:42:25</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:54:20</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>韦家鹏</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:53:08</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>postponed</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>42406</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>系统迁移（自定义）</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>【自定义迁移】关于自定义迁移点击官网下载失效的问题</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:40:52</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:44:46</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:18:10</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:44:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>42405</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>分区拷贝</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>【分区克隆】关于扇区级克隆BitLocker分区时，未提示不保留BitLocker的提示（自动化）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:49:26</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:22:42</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:20:16</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>42408</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.2.0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.2</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>关于广告入口版本限制问题</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 10:09:47</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:28:11</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:18:16</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:28:11</t>
         </is>
       </c>
     </row>

--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42403</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EPM20.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>关于关闭活动条后，图片变更不会再出触发活动条的问题</t>
+          <t>关于调用Migrate无效问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -593,37 +593,37 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:22:51</t>
+          <t>2026-05-09 09:34:22</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 09:45:08</t>
+          <t>2026-05-09 10:19:08</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 09:43:02</t>
+          <t>2026-05-09 10:18:13</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
@@ -636,7 +636,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>42413</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EPM20.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>EPM20.2</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>关于arm设备没有屏蔽bootable media入口问题</t>
+          <t>关于空间分析取值错误问题</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -681,13 +681,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:01</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+          <t>2026-05-09 09:25:09</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 17:43:39</t>
+          <t>2026-05-09 09:51:14</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -697,7 +701,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 13:51:09</t>
+          <t>2026-05-09 09:50:55</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -705,21 +709,17 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 17:43:39</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42327</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>网络克隆</t>
+          <t>PE制作</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>【网络克隆】关于网络克隆许可扣减后，在关于中的可用数量不变的问题</t>
+          <t>【PE制作】关于制作PE后，未对PE进行解压的问题</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -754,33 +754,37 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01 10:32:10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>2026-04-14 17:34:28</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 10:10:16</t>
+          <t>2026-05-08 18:31:50</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>陈明</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 13:06:56</t>
+          <t>2026-05-08 18:31:14</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -788,41 +792,37 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>李俊杰</t>
-        </is>
-      </c>
+      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 10:10:16</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>网络克隆</t>
+          <t>活动入口</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>【网络克隆】关于server部署在公网服务器上时，显示下载client的地址为私有IP的问题</t>
+          <t>关于关闭活动条后，图片变更不会再出触发活动条的问题</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14 14:15:10</t>
+          <t>2026-04-29 18:22:51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:41:27</t>
+          <t>2026-05-08 09:45:08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:40:53</t>
+          <t>2026-05-08 09:43:02</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>postponed</t>
+          <t>bydesign</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
@@ -885,90 +885,94 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>42410</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>系统克隆</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>【系统克隆】关于GPT系统克隆后，未修改BCD的问题（老问题）</t>
+          <t>关于arm设备没有屏蔽bootable media入口问题</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 13:42:25</t>
+          <t>2026-05-07 10:30:01</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:54:20</t>
+          <t>2026-05-09 09:20:51</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:53:08</t>
+          <t>2026-05-07 13:51:09</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>postponed</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-07 17:43:39</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42256</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -983,12 +987,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>系统迁移（自定义）</t>
+          <t>网络克隆</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>【自定义迁移】关于自定义迁移点击官网下载失效的问题</t>
+          <t>【网络克隆】关于网络克隆许可扣减后，在关于中的可用数量不变的问题</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1013,13 +1017,13 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 13:40:52</t>
+          <t>2026-04-01 10:32:10</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:44:46</t>
+          <t>2026-05-08 10:10:16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1029,7 +1033,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:18:10</t>
+          <t>2026-05-07 13:06:56</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1044,14 +1048,14 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:44:46</t>
+          <t>2026-05-08 10:10:16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42322</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1066,12 +1070,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>分区拷贝</t>
+          <t>网络克隆</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>【分区克隆】关于扇区级克隆BitLocker分区时，未提示不保留BitLocker的提示（自动化）</t>
+          <t>【网络克隆】关于server部署在公网服务器上时，显示下载client的地址为私有IP的问题</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1096,32 +1100,32 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 09:49:26</t>
+          <t>2026-04-14 14:15:10</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>韦家鹏</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 11:22:42</t>
+          <t>2026-05-07 10:41:27</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>贺照云</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 11:20:16</t>
+          <t>2026-05-07 10:40:53</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>postponed</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1134,81 +1138,334 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>42407</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>系统克隆</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>【系统克隆】关于GPT系统克隆后，未修改BCD的问题（老问题）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:42:25</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:54:20</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>韦家鹏</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:53:08</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>postponed</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>42406</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>系统迁移（自定义）</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>【自定义迁移】关于自定义迁移点击官网下载失效的问题</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:40:52</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:44:46</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:18:10</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:44:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>42405</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>分区拷贝</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>【分区克隆】关于扇区级克隆BitLocker分区时，未提示不保留BitLocker的提示（自动化）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:49:26</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:04:56</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:20:16</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:04:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>42408</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>EPM</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.2.0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.2</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>活动入口</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>关于广告入口版本限制问题</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>2026-05-06 10:09:47</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06 17:28:11</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:21:40</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>彭均</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2026-05-06 11:18:16</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2026-05-06 17:28:11</t>
         </is>

--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42415</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>关于调用Migrate无效问题</t>
+          <t>当epm切换过语言后，点击scan后ecg有概率会崩溃</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -593,22 +593,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:34:22</t>
+          <t>2026-05-11 09:46:44</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 10:19:08</t>
+          <t>2026-05-11 14:40:22</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 10:18:13</t>
+          <t>2026-05-11 14:39:49</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>42413</t>
+          <t>42441</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>关于空间分析取值错误问题</t>
+          <t>关于启动epm后去调用ecg进程有概率自动结束问题</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:25:09</t>
+          <t>2026-05-09 16:30:47</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:14</t>
+          <t>2026-05-11 14:38:46</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:50:55</t>
+          <t>2026-05-11 14:38:41</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -719,27 +719,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PE制作</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>【PE制作】关于制作PE后，未对PE进行解压的问题</t>
+          <t>关于空间清理调用ECG可能会失败的问题</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -759,32 +759,32 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14 17:34:28</t>
+          <t>2026-05-09 10:12:59</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 18:31:50</t>
+          <t>2026-05-11 14:38:38</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>陈明</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 18:31:14</t>
+          <t>2026-05-11 14:37:11</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>42403</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>活动入口</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>关于关闭活动条后，图片变更不会再出触发活动条的问题</t>
+          <t>关于Space Analysis删除文件后刷新，剩余空间和文件显示不正确的问题</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -847,32 +847,32 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:22:51</t>
+          <t>2026-05-09 13:35:43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 09:45:08</t>
+          <t>2026-05-11 14:35:28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 09:43:02</t>
+          <t>2026-05-11 14:34:36</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
@@ -885,7 +885,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>42438</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>关于arm设备没有屏蔽bootable media入口问题</t>
+          <t>关于ecg卸载应用后epm没有进行自动刷新</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:01</t>
+          <t>2026-05-09 16:11:28</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -940,17 +940,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:20:51</t>
+          <t>2026-05-10 14:50:42</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 13:51:09</t>
+          <t>2026-05-10 14:50:20</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -958,41 +958,37 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 17:43:39</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>网络克隆</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>【网络克隆】关于网络克隆许可扣减后，在关于中的可用数量不变的问题</t>
+          <t>关于EPM启动时语言会跟随Space Analysis变化的问题</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1007,33 +1003,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01 10:32:10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>2026-05-09 13:59:22</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 10:10:16</t>
+          <t>2026-05-10 14:36:43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 13:06:56</t>
+          <t>2026-05-10 14:34:19</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1041,41 +1041,37 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>李俊杰</t>
-        </is>
-      </c>
+      <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 10:10:16</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>网络克隆</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>【网络克隆】关于server部署在公网服务器上时，显示下载client的地址为私有IP的问题</t>
+          <t>EPM调用空间分析和ECG后，关闭epm自动关闭了二个子进程</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1095,37 +1091,37 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14 14:15:10</t>
+          <t>2026-05-09 16:10:31</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:41:27</t>
+          <t>2026-05-10 14:31:39</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:40:53</t>
+          <t>2026-05-10 14:30:39</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>postponed</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1138,37 +1134,37 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>42434</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>系统克隆</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>【系统克隆】关于GPT系统克隆后，未修改BCD的问题（老问题）</t>
+          <t>关于没有取到数据时显示不正确问题</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1178,37 +1174,37 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 13:42:25</t>
+          <t>2026-05-09 15:31:46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:54:20</t>
+          <t>2026-05-10 14:11:33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:53:08</t>
+          <t>2026-05-10 14:10:33</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>postponed</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -1221,27 +1217,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>系统迁移（自定义）</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>【自定义迁移】关于自定义迁移点击官网下载失效的问题</t>
+          <t>关于字体效果显示问题</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1256,33 +1252,37 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 13:40:52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>2026-05-09 16:37:10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:44:46</t>
+          <t>2026-05-09 16:50:09</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:18:10</t>
+          <t>2026-05-09 16:49:43</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1290,41 +1290,37 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>李俊杰</t>
-        </is>
-      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:44:46</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>分区拷贝</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>【分区克隆】关于扇区级克隆BitLocker分区时，未提示不保留BitLocker的提示（自动化）</t>
+          <t>关于space Analyze本地安装和程序调用的是同一个进程</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1339,33 +1335,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 09:49:26</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>2026-05-09 14:13:47</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:56</t>
+          <t>2026-05-09 16:38:50</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 11:20:16</t>
+          <t>2026-05-09 16:38:00</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1373,99 +1373,1178 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>杨光雪</t>
-        </is>
-      </c>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:56</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>42439</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>关于Clean页面数据迁移图标浅色主题下显示缺失的问题</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:12:19</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:33:54</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 16:33:42</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>42430</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>关于调用本地的ecg会将自带的程序置顶了后才调用</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:35:28</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:51:22</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 15:51:00</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>duplicate</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>42416</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>当系统托盘有常驻的ecg时，点击clean入口后就直接调用了ECG主窗口</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>刘冬</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:51:47</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>刘冬</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:13:09</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:11:57</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>42415</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>关于调用Migrate无效问题</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:34:22</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 10:19:08</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 10:18:13</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>42413</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>空间管理</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>关于空间分析取值错误问题</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:25:09</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:51:14</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:50:55</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>42327</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PE制作</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>【PE制作】关于制作PE后，未对PE进行解压的问题</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14 17:34:28</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:31:50</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>陈明</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:31:14</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>42403</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>活动入口</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>关于关闭活动条后，图片变更不会再出触发活动条的问题</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:22:51</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>韦家鹏</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:45:08</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:43:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>bydesign</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>42410</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>关于arm设备没有屏蔽bootable media入口问题</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:30:01</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 09:20:51</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:51:09</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 17:43:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>42256</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>网络克隆</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>【网络克隆】关于网络克隆许可扣减后，在关于中的可用数量不变的问题</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:32:10</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:10:16</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 13:06:56</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:10:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>42322</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>网络克隆</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>【网络克隆】关于server部署在公网服务器上时，显示下载client的地址为私有IP的问题</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14 14:15:10</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>韦家鹏</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:41:27</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:40:53</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>postponed</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>42407</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>系统克隆</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>【系统克隆】关于GPT系统克隆后，未修改BCD的问题（老问题）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:42:25</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:54:20</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>韦家鹏</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:53:08</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>postponed</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>42406</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>系统迁移（自定义）</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>【自定义迁移】关于自定义迁移点击官网下载失效的问题</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:40:52</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:44:46</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 13:18:10</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>李俊杰</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 10:44:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>42405</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Disk Copy</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>DC7.2.0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>分区拷贝</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>【分区克隆】关于扇区级克隆BitLocker分区时，未提示不保留BitLocker的提示（自动化）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:49:26</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:04:56</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>姜飞</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:20:16</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:04:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>42408</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>EPM</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>EPM20.5.0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>活动入口</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>关于广告入口版本限制问题</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>2026-05-06 10:09:47</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>2026-05-09 09:21:40</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>彭均</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2026-05-06 11:18:16</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2026-05-06 17:28:11</t>
         </is>

--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -441,13 +441,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -458,7 +458,7 @@
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
   </cols>
@@ -553,27 +553,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EPM</t>
+          <t>Disk Copy</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5.0</t>
+          <t>DC7.4.0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>激活</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>当epm切换过语言后，点击scan后ecg有概率会崩溃</t>
+          <t>【激活】关于拦截界面的Business购买链接仍是Home版本链接的问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -593,32 +593,32 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 09:46:44</t>
+          <t>2026-05-20 14:06:57</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 14:40:22</t>
+          <t>2026-05-20 14:28:11</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>郑浪</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 14:39:49</t>
+          <t>2026-05-20 14:24:58</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>关于启动epm后去调用ecg进程有概率自动结束问题</t>
+          <t>【遗留】动态盘创建分区界面显示异常</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:30:47</t>
+          <t>2026-05-11 14:37:07</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 14:38:46</t>
+          <t>2026-05-20 10:24:43</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 14:38:41</t>
+          <t>2026-05-20 10:24:18</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>关于空间清理调用ECG可能会失败的问题</t>
+          <t>关于Migrate Data完成后，Clean页面数据未跟随刷新的问题</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -764,45 +764,45 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 10:12:59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+          <t>2026-05-15 11:26:25</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:39:56</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 10:00:07</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>何峻</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:38:38</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:37:11</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 14:39:56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>42457</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>关于Space Analysis删除文件后刷新，剩余空间和文件显示不正确的问题</t>
+          <t>关于部分分辨率下，Clean页面显示不完全，且无法扩大窗口的问题</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -847,45 +847,45 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 13:35:43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+          <t>2026-05-12 10:14:34</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:17:48</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 16:03:22</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>何峻</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:35:28</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:34:36</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 09:17:48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>42438</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>关于ecg卸载应用后epm没有进行自动刷新</t>
+          <t>关于切换导航栏时会自动调用ecg问题</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -930,45 +930,45 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:11:28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+          <t>2026-05-19 11:29:36</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:46:14</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:56:46</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10 14:50:42</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10 14:50:20</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 14:46:14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>关于EPM启动时语言会跟随Space Analysis变化的问题</t>
+          <t>关于clean模块手动刷新会导致界面闪烁问题</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1008,22 +1008,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 13:59:22</t>
+          <t>2026-05-19 13:27:23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10 14:36:43</t>
+          <t>2026-05-19 14:56:44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10 14:34:19</t>
+          <t>2026-05-19 14:49:32</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>EPM调用空间分析和ECG后，关闭epm自动关闭了二个子进程</t>
+          <t>已使用空间的表述不合理</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:10:31</t>
+          <t>2026-05-09 14:26:46</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10 14:31:39</t>
+          <t>2026-05-19 14:04:38</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10 14:30:39</t>
+          <t>2026-05-19 14:04:30</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>42434</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>关于没有取到数据时显示不正确问题</t>
+          <t>关于空间分析部分数据百分比显示异常的问题</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1174,32 +1174,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 15:31:46</t>
+          <t>2026-05-19 11:33:42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10 14:11:33</t>
+          <t>2026-05-19 13:54:48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10 14:10:33</t>
+          <t>2026-05-19 13:46:34</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>关于字体效果显示问题</t>
+          <t>关于在clean页面调用起了space analyze和ecg后discovery页面无法下载程序问题</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1262,45 +1262,45 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:37:10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+          <t>2026-05-14 11:25:18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:30:02</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:49:56</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 16:50:09</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>彭均</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 16:49:43</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 14:30:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>42428</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>关于space Analyze本地安装和程序调用的是同一个进程</t>
+          <t>关于切换频道后clean不会自动刷新问题</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1345,45 +1345,45 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:13:47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+          <t>2026-05-14 11:09:09</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 14:29:50</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>彭均</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 17:08:54</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 16:38:50</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 16:38:00</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 14:29:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>42439</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>关于Clean页面数据迁移图标浅色主题下显示缺失的问题</t>
+          <t>关于ecg清理了数据后EPM的Reclaimable值不会更新问题</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1418,37 +1418,33 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:12:19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
+          <t>2026-05-18 13:48:04</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:33:54</t>
+          <t>2026-05-19 17:22:41</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 16:33:42</t>
+          <t>2026-05-18 15:39:34</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1456,17 +1452,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-19 17:22:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>42430</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>关于调用本地的ecg会将自带的程序置顶了后才调用</t>
+          <t>关于junk files在删除数据后没有跟新信息问题</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1511,45 +1511,45 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:35:28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+          <t>2026-05-18 13:34:37</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:31</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:37:54</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 15:51:22</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 15:51:00</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>duplicate</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-19 17:22:31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>42416</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>当系统托盘有常驻的ecg时，点击clean入口后就直接调用了ECG主窗口</t>
+          <t>关于Space Analyzer在调用情况下，下载安装提示进程存在问题</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1589,22 +1589,22 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:47</t>
+          <t>2026-05-18 10:53:30</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 13:13:09</t>
+          <t>2026-05-18 15:09:47</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 13:11:57</t>
+          <t>2026-05-18 15:08:39</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>42415</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>关于调用Migrate无效问题</t>
+          <t>关于win7环境下，通过Clean调ECG无法跳转指定页面和无法自动扫描的问题</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1667,27 +1667,23 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:34:22</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+          <t>2026-05-18 09:46:35</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 10:19:08</t>
+          <t>2026-05-20 09:57:26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1697,7 +1693,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 10:18:13</t>
+          <t>2026-05-18 14:17:57</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1705,17 +1701,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 09:57:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>42413</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>关于空间分析取值错误问题</t>
+          <t>关于Clean-空间分析Folder部分内容显示异常的问题</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1750,37 +1750,33 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:25:09</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+          <t>2026-05-15 10:10:27</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:51:14</t>
+          <t>2026-05-20 09:35:10</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>谢蜀岷</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:50:55</t>
+          <t>2026-05-18 13:02:20</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1788,37 +1784,41 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 09:35:10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PE制作</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>【PE制作】关于制作PE后，未对PE进行解压的问题</t>
+          <t>关于Space Analyze 进度显示问题</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1833,55 +1833,55 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14 17:34:28</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>杨光雪</t>
-        </is>
-      </c>
+          <t>2026-05-15 10:43:20</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 18:31:50</t>
+          <t>2026-05-19 17:21:58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>陈明</t>
+          <t>谢蜀岷</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 18:31:14</t>
+          <t>2026-05-18 10:14:24</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t>bydesign</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-19 17:21:58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>42403</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>活动入口</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>关于关闭活动条后，图片变更不会再出触发活动条的问题</t>
+          <t>关于空间清理扫描没有设置超时的问题</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1926,32 +1926,32 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:22:51</t>
+          <t>2026-05-13 17:03:58</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>邓贵星</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 09:45:08</t>
+          <t>2026-05-18 10:16:03</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>贺照云</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 09:43:02</t>
+          <t>2026-05-15 17:18:10</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
+          <t>willnotfix</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr"/>
@@ -1964,7 +1964,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>42410</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>活动入口</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>关于arm设备没有屏蔽bootable media入口问题</t>
+          <t>关于hover 图片异常时也能进行入口显示问题</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2009,69 +2009,65 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:30:01</t>
+          <t>2026-05-06 14:02:34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>贺照云</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 09:20:51</t>
+          <t>2026-05-15 16:28:19</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>韦家鹏</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 13:51:09</t>
+          <t>2026-05-15 16:27:46</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+          <t>nonproblem</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 17:43:39</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>网络克隆</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>【网络克隆】关于网络克隆许可扣减后，在关于中的可用数量不变的问题</t>
+          <t>关于ecg本地和自带的数据扫描出来不一致问题</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2091,28 +2087,28 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01 10:32:10</t>
+          <t>2026-05-15 11:13:48</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 10:10:16</t>
+          <t>2026-05-19 17:22:20</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 13:06:56</t>
+          <t>2026-05-15 14:22:07</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2122,39 +2118,39 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08 10:10:16</t>
+          <t>2026-05-19 17:22:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>42432</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>网络克隆</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>【网络克隆】关于server部署在公网服务器上时，显示下载client的地址为私有IP的问题</t>
+          <t>点击scan调用ecg后，经常出现任务栏图标显示不出来的现象</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2174,37 +2170,37 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14 14:15:10</t>
+          <t>2026-05-09 14:54:25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:41:27</t>
+          <t>2026-05-15 09:35:23</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:40:53</t>
+          <t>2026-05-15 09:30:45</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>postponed</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr"/>
@@ -2217,110 +2213,110 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>系统克隆</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>【系统克隆】关于GPT系统克隆后，未修改BCD的问题（老问题）</t>
+          <t>关于调整C分区大小后，空间清理会闪退的问题</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 13:42:25</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>贺照云</t>
-        </is>
-      </c>
+          <t>2026-05-13 13:39:39</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:54:20</t>
+          <t>2026-05-18 14:31:21</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:53:08</t>
+          <t>2026-05-14 15:13:06</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>postponed</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-18 14:31:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>42406</t>
+          <t>42445</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DC7.2.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>系统迁移（自定义）</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>【自定义迁移】关于自定义迁移点击官网下载失效的问题</t>
+          <t>关于在win7环境下Clean页面调用然后关闭内置空间分析，报错的问题</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2340,28 +2336,28 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30 13:40:52</t>
+          <t>2026-05-11 09:30:30</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:44:46</t>
+          <t>2026-05-18 09:30:40</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>姜飞</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 13:18:10</t>
+          <t>2026-05-14 15:10:09</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2371,182 +2367,12 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-07 10:44:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>42405</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Disk Copy</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>DC7.2.0</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>分区拷贝</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>【分区克隆】关于扇区级克隆BitLocker分区时，未提示不保留BitLocker的提示（自动化）</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>杨光雪</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30 09:49:26</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08 16:04:56</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>姜飞</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06 11:20:16</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>杨光雪</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08 16:04:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>42408</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>活动入口</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>关于广告入口版本限制问题</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06 10:09:47</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09 09:21:40</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>彭均</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06 11:18:16</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-06 17:28:11</t>
+          <t>2026-05-18 09:30:40</t>
         </is>
       </c>
     </row>

--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1016,35 +1016,35 @@
           <t>2026-05-19 13:27:23</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:27:09</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 14:49:32</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19 14:56:44</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-19 14:49:32</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 17:27:09</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1597,35 +1597,35 @@
           <t>2026-05-18 10:53:30</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:13:40</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 15:08:39</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>辜健</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 15:09:47</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 15:08:39</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 17:13:40</t>
         </is>
       </c>
     </row>

--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,27 +553,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DC7.4.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>激活</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>【激活】关于拦截界面的Business购买链接仍是Home版本链接的问题</t>
+          <t>关于部分环境偶现初次扫描垃圾文件大小与实际不符的问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -588,37 +588,33 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:06:57</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>杨光雪</t>
-        </is>
-      </c>
+          <t>2026-05-15 15:51:50</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:28:11</t>
+          <t>2026-05-21 15:34:40</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>郑浪</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:24:58</t>
+          <t>2026-05-20 17:36:53</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -626,37 +622,41 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-21 15:34:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>EPM</t>
+          <t>Disk Copy</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5.0</t>
+          <t>DC7.4.0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>激活</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>【遗留】动态盘创建分区界面显示异常</t>
+          <t>【激活】关于拦截界面的Business购买链接仍是Home版本链接的问题</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -676,32 +676,32 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 14:37:07</t>
+          <t>2026-05-20 14:06:57</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 10:24:43</t>
+          <t>2026-05-20 14:28:11</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>郑浪</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 10:24:18</t>
+          <t>2026-05-20 14:24:58</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>关于Migrate Data完成后，Clean页面数据未跟随刷新的问题</t>
+          <t>【遗留】动态盘创建分区界面显示异常</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -754,23 +754,27 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 11:26:25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+          <t>2026-05-11 14:37:07</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:39:56</t>
+          <t>2026-05-20 10:24:43</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +784,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 10:00:07</t>
+          <t>2026-05-20 10:24:18</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -788,21 +792,17 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
+      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:39:56</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>关于部分分辨率下，Clean页面显示不完全，且无法扩大窗口的问题</t>
+          <t>关于Migrate Data完成后，Clean页面数据未跟随刷新的问题</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -847,13 +847,13 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 10:14:34</t>
+          <t>2026-05-15 11:26:25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:48</t>
+          <t>2026-05-20 14:39:56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 16:03:22</t>
+          <t>2026-05-20 10:00:07</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -878,14 +878,14 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:48</t>
+          <t>2026-05-20 14:39:56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42457</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>关于切换导航栏时会自动调用ecg问题</t>
+          <t>关于部分分辨率下，Clean页面显示不完全，且无法扩大窗口的问题</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -925,28 +925,28 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:29:36</t>
+          <t>2026-05-12 10:14:34</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:46:14</t>
+          <t>2026-05-20 09:17:48</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:56:46</t>
+          <t>2026-05-19 16:03:22</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -956,19 +956,19 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:46:14</t>
+          <t>2026-05-20 09:17:48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>关于clean模块手动刷新会导致界面闪烁问题</t>
+          <t>关于切换导航栏时会自动调用ecg问题</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1013,13 +1013,13 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:27:23</t>
+          <t>2026-05-19 11:29:36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:27:09</t>
+          <t>2026-05-20 14:46:14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:49:32</t>
+          <t>2026-05-19 14:56:46</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1044,14 +1044,14 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:27:09</t>
+          <t>2026-05-20 14:46:14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>已使用空间的表述不合理</t>
+          <t>关于clean模块手动刷新会导致界面闪烁问题</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1086,37 +1086,33 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:26:46</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>刘冬</t>
-        </is>
-      </c>
+          <t>2026-05-19 13:27:23</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:04:38</t>
+          <t>2026-05-20 17:27:09</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:04:30</t>
+          <t>2026-05-19 14:49:32</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1124,17 +1120,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 17:27:09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>关于空间分析部分数据百分比显示异常的问题</t>
+          <t>已使用空间的表述不合理</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1174,32 +1174,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:33:42</t>
+          <t>2026-05-09 14:26:46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:54:48</t>
+          <t>2026-05-19 14:04:38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:46:34</t>
+          <t>2026-05-19 14:04:30</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>关于在clean页面调用起了space analyze和ecg后discovery页面无法下载程序问题</t>
+          <t>关于空间分析部分数据百分比显示异常的问题</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1257,18 +1257,18 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14 11:25:18</t>
+          <t>2026-05-19 11:33:42</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:30:02</t>
+          <t>2026-05-21 15:34:51</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 10:49:56</t>
+          <t>2026-05-19 13:46:34</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:30:02</t>
+          <t>2026-05-21 15:34:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>关于切换频道后clean不会自动刷新问题</t>
+          <t>关于在clean页面调用起了space analyze和ecg后discovery页面无法下载程序问题</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1345,23 +1345,23 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14 11:09:09</t>
+          <t>2026-05-14 11:25:18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:29:50</t>
+          <t>2026-05-20 14:30:02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:08:54</t>
+          <t>2026-05-19 10:49:56</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1376,14 +1376,14 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:29:50</t>
+          <t>2026-05-20 14:30:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>关于ecg清理了数据后EPM的Reclaimable值不会更新问题</t>
+          <t>关于切换频道后clean不会自动刷新问题</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1428,23 +1428,23 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:48:04</t>
+          <t>2026-05-14 11:09:09</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:41</t>
+          <t>2026-05-20 14:29:50</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:39:34</t>
+          <t>2026-05-18 17:08:54</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:41</t>
+          <t>2026-05-20 14:29:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>关于junk files在删除数据后没有跟新信息问题</t>
+          <t>关于ecg清理了数据后EPM的Reclaimable值不会更新问题</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1511,13 +1511,13 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:34:37</t>
+          <t>2026-05-18 13:48:04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:31</t>
+          <t>2026-05-19 17:22:41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:37:54</t>
+          <t>2026-05-18 15:39:34</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1542,14 +1542,14 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:31</t>
+          <t>2026-05-19 17:22:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>关于Space Analyzer在调用情况下，下载安装提示进程存在问题</t>
+          <t>关于junk files在删除数据后没有跟新信息问题</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1594,13 +1594,13 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:53:30</t>
+          <t>2026-05-18 13:34:37</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:13:40</t>
+          <t>2026-05-19 17:22:31</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:08:39</t>
+          <t>2026-05-18 15:37:54</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1625,14 +1625,14 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:13:40</t>
+          <t>2026-05-19 17:22:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>关于win7环境下，通过Clean调ECG无法跳转指定页面和无法自动扫描的问题</t>
+          <t>关于Space Analyzer在调用情况下，下载安装提示进程存在问题</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1672,18 +1672,18 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:46:35</t>
+          <t>2026-05-18 10:53:30</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:57:26</t>
+          <t>2026-05-20 17:13:40</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 14:17:57</t>
+          <t>2026-05-18 15:08:39</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1703,19 +1703,19 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:57:26</t>
+          <t>2026-05-20 17:13:40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>关于Clean-空间分析Folder部分内容显示异常的问题</t>
+          <t>关于win7环境下，通过Clean调ECG无法跳转指定页面和无法自动扫描的问题</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1760,23 +1760,23 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 10:10:27</t>
+          <t>2026-05-18 09:46:35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:35:10</t>
+          <t>2026-05-20 09:57:26</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>谢蜀岷</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:02:20</t>
+          <t>2026-05-18 14:17:57</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:35:10</t>
+          <t>2026-05-20 09:57:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>关于Space Analyze 进度显示问题</t>
+          <t>关于Clean-空间分析Folder部分内容显示异常的问题</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1838,18 +1838,18 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 10:43:20</t>
+          <t>2026-05-15 10:10:27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:21:58</t>
+          <t>2026-05-20 09:35:10</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1859,29 +1859,29 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:14:24</t>
+          <t>2026-05-18 13:02:20</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:21:58</t>
+          <t>2026-05-20 09:35:10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>关于空间清理扫描没有设置超时的问题</t>
+          <t>关于Space Analyze 进度显示问题</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1916,55 +1916,55 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 17:03:58</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>邓贵星</t>
-        </is>
-      </c>
+          <t>2026-05-15 10:43:20</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:16:03</t>
+          <t>2026-05-19 17:21:58</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>谢蜀岷</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 17:18:10</t>
+          <t>2026-05-18 10:14:24</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>willnotfix</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t>bydesign</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-19 17:21:58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>活动入口</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>关于hover 图片异常时也能进行入口显示问题</t>
+          <t>关于空间清理扫描没有设置超时的问题</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2004,37 +2004,37 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:34</t>
+          <t>2026-05-13 17:03:58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
+          <t>邓贵星</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 10:16:03</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
           <t>贺照云</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15 16:28:19</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>韦家鹏</t>
-        </is>
-      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 16:27:46</t>
+          <t>2026-05-15 17:18:10</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>nonproblem</t>
+          <t>willnotfix</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>活动入口</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>关于ecg本地和自带的数据扫描出来不一致问题</t>
+          <t>关于hover 图片异常时也能进行入口显示问题</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2092,45 +2092,45 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 11:13:48</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+          <t>2026-05-06 14:02:34</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:20</t>
+          <t>2026-05-15 16:28:19</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>韦家鹏</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 14:22:07</t>
+          <t>2026-05-15 16:27:46</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+          <t>nonproblem</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:20</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>点击scan调用ecg后，经常出现任务栏图标显示不出来的现象</t>
+          <t>关于ecg本地和自带的数据扫描出来不一致问题</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2165,27 +2165,23 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:54:25</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>刘冬</t>
-        </is>
-      </c>
+          <t>2026-05-15 11:13:48</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 09:35:23</t>
+          <t>2026-05-19 17:22:20</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2195,7 +2191,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 09:30:45</t>
+          <t>2026-05-15 14:22:07</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2203,17 +2199,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-19 17:22:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>42459</t>
+          <t>42432</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>关于调整C分区大小后，空间清理会闪退的问题</t>
+          <t>点击scan调用ecg后，经常出现任务栏图标显示不出来的现象</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2248,23 +2248,27 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 13:39:39</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+          <t>2026-05-09 14:54:25</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>刘冬</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 14:31:21</t>
+          <t>2026-05-15 09:35:23</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2274,7 +2278,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14 15:13:06</t>
+          <t>2026-05-15 09:30:45</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2282,97 +2286,10 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
+      <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 14:31:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>42445</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>EPM</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EPM20.5.0</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>空间管理</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>关于在win7环境下Clean页面调用然后关闭内置空间分析，报错的问题</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11 09:30:30</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 09:30:40</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>余悦</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-14 15:10:09</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18 09:30:40</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>

--- a/monitor-zentao/code/currentbug.xlsx
+++ b/monitor-zentao/code/currentbug.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5.0</t>
+          <t>EPM20.2.0</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>历史遗留</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>关于部分环境偶现初次扫描垃圾文件大小与实际不符的问题</t>
+          <t>【遗留】【自动化】关于低格完成后快速分区时程序崩溃的问题</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -598,23 +598,23 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 15:51:50</t>
+          <t>2026-05-09 17:45:33</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:34:40</t>
+          <t>2026-05-22 11:16:22</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:36:53</t>
+          <t>2026-05-22 11:10:57</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -629,34 +629,34 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:34:40</t>
+          <t>2026-05-22 11:16:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42424</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Disk Copy</t>
+          <t>EPM</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DC7.4.0</t>
+          <t>EPM20.5.0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>激活</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>【激活】关于拦截界面的Business购买链接仍是Home版本链接的问题</t>
+          <t>关于调用的ecg和Analyze没有改名问题</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -676,32 +676,32 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:06:57</t>
+          <t>2026-05-09 13:33:47</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>杨光雪</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:28:11</t>
+          <t>2026-05-22 11:05:06</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>郑浪</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:24:58</t>
+          <t>2026-05-22 11:04:28</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>其它</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>【遗留】动态盘创建分区界面显示异常</t>
+          <t>关于右侧Adjust Disk Layout会置灰无法点击的问题</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -754,27 +754,23 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11 14:37:07</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+          <t>2026-05-21 15:38:32</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 10:24:43</t>
+          <t>2026-05-22 11:06:03</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -784,7 +780,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 10:24:18</t>
+          <t>2026-05-21 16:24:16</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -792,17 +788,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-22 11:06:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>关于Migrate Data完成后，Clean页面数据未跟随刷新的问题</t>
+          <t>关于部分环境偶现初次扫描垃圾文件大小与实际不符的问题</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -847,23 +847,23 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 11:26:25</t>
+          <t>2026-05-15 15:51:50</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:39:56</t>
+          <t>2026-05-21 15:34:40</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 10:00:07</t>
+          <t>2026-05-20 17:36:53</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -878,34 +878,34 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:39:56</t>
+          <t>2026-05-21 15:34:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>42457</t>
+          <t>42482</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EPM</t>
+          <t>Disk Copy</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5.0</t>
+          <t>DC7.4.0</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>激活</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>关于部分分辨率下，Clean页面显示不完全，且无法扩大窗口的问题</t>
+          <t>【激活】关于拦截界面的Business购买链接仍是Home版本链接的问题</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -920,33 +920,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>杨光雪</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12 10:14:34</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+          <t>2026-05-20 14:06:57</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>杨光雪</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:48</t>
+          <t>2026-05-20 14:28:11</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>彭均</t>
+          <t>郑浪</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 16:03:22</t>
+          <t>2026-05-20 14:24:58</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -954,21 +958,17 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>何峻</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:17:48</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>关于切换导航栏时会自动调用ecg问题</t>
+          <t>【遗留】动态盘创建分区界面显示异常</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1013,23 +1013,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:29:36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+          <t>2026-05-11 14:37:07</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:46:14</t>
+          <t>2026-05-20 10:24:43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:56:46</t>
+          <t>2026-05-20 10:24:18</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1037,21 +1041,17 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+      <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:46:14</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>关于clean模块手动刷新会导致界面闪烁问题</t>
+          <t>关于Migrate Data完成后，Clean页面数据未跟随刷新的问题</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1091,28 +1091,28 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:27:23</t>
+          <t>2026-05-15 11:26:25</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:27:09</t>
+          <t>2026-05-20 14:39:56</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:49:32</t>
+          <t>2026-05-20 10:00:07</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1122,19 +1122,19 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:27:09</t>
+          <t>2026-05-20 14:39:56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>42457</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>已使用空间的表述不合理</t>
+          <t>关于部分分辨率下，Clean页面显示不完全，且无法扩大窗口的问题</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1169,27 +1169,23 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:26:46</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>刘冬</t>
-        </is>
-      </c>
+          <t>2026-05-12 10:14:34</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:04:38</t>
+          <t>2026-05-20 09:17:48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 14:04:30</t>
+          <t>2026-05-19 16:03:22</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1207,17 +1203,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 09:17:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>关于空间分析部分数据百分比显示异常的问题</t>
+          <t>关于切换导航栏时会自动调用ecg问题</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1257,18 +1257,18 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 11:33:42</t>
+          <t>2026-05-19 11:29:36</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:34:51</t>
+          <t>2026-05-20 14:46:14</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 13:46:34</t>
+          <t>2026-05-19 14:56:46</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1288,19 +1288,19 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21 15:34:51</t>
+          <t>2026-05-20 14:46:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>关于在clean页面调用起了space analyze和ecg后discovery页面无法下载程序问题</t>
+          <t>关于clean模块手动刷新会导致界面闪烁问题</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1345,13 +1345,13 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14 11:25:18</t>
+          <t>2026-05-19 13:27:23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:30:02</t>
+          <t>2026-05-20 17:27:09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 10:49:56</t>
+          <t>2026-05-19 14:49:32</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1376,14 +1376,14 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:30:02</t>
+          <t>2026-05-20 17:27:09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>关于切换频道后clean不会自动刷新问题</t>
+          <t>已使用空间的表述不合理</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1418,23 +1418,27 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>刘冬</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14 11:09:09</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+          <t>2026-05-09 14:26:46</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>刘冬</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:29:50</t>
+          <t>2026-05-19 14:04:38</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1444,7 +1448,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 17:08:54</t>
+          <t>2026-05-19 14:04:30</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1452,21 +1456,17 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>辜健</t>
-        </is>
-      </c>
+      <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 14:29:50</t>
+          <t>0000-00-00 00:00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>关于ecg清理了数据后EPM的Reclaimable值不会更新问题</t>
+          <t>关于空间分析部分数据百分比显示异常的问题</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1506,18 +1506,18 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:48:04</t>
+          <t>2026-05-19 11:33:42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:41</t>
+          <t>2026-05-21 15:34:51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:39:34</t>
+          <t>2026-05-19 13:46:34</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1537,19 +1537,19 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:41</t>
+          <t>2026-05-21 15:34:51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>关于junk files在删除数据后没有跟新信息问题</t>
+          <t>关于在clean页面调用起了space analyze和ecg后discovery页面无法下载程序问题</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1594,13 +1594,13 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:34:37</t>
+          <t>2026-05-14 11:25:18</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:31</t>
+          <t>2026-05-20 14:30:02</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:37:54</t>
+          <t>2026-05-19 10:49:56</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1625,14 +1625,14 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:31</t>
+          <t>2026-05-20 14:30:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>空间管理</t>
+          <t>EPM20.5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>关于Space Analyzer在调用情况下，下载安装提示进程存在问题</t>
+          <t>关于切换频道后clean不会自动刷新问题</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1677,23 +1677,23 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:53:30</t>
+          <t>2026-05-14 11:09:09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:13:40</t>
+          <t>2026-05-20 14:29:50</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>彭均</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 15:08:39</t>
+          <t>2026-05-18 17:08:54</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1708,14 +1708,14 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 17:13:40</t>
+          <t>2026-05-20 14:29:50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>关于win7环境下，通过Clean调ECG无法跳转指定页面和无法自动扫描的问题</t>
+          <t>关于ecg清理了数据后EPM的Reclaimable值不会更新问题</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1755,18 +1755,18 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 09:46:35</t>
+          <t>2026-05-18 13:48:04</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:57:26</t>
+          <t>2026-05-19 17:22:41</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 14:17:57</t>
+          <t>2026-05-18 15:39:34</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1786,19 +1786,19 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:57:26</t>
+          <t>2026-05-19 17:22:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>关于Clean-空间分析Folder部分内容显示异常的问题</t>
+          <t>关于junk files在删除数据后没有跟新信息问题</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1838,28 +1838,28 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 10:10:27</t>
+          <t>2026-05-18 13:34:37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:35:10</t>
+          <t>2026-05-19 17:22:31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>谢蜀岷</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 13:02:20</t>
+          <t>2026-05-18 15:37:54</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1869,19 +1869,19 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>何峻</t>
+          <t>辜健</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-20 09:35:10</t>
+          <t>2026-05-19 17:22:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>42469</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>EPM20.5</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>关于Space Analyze 进度显示问题</t>
+          <t>关于Space Analyzer在调用情况下，下载安装提示进程存在问题</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1926,28 +1926,28 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 10:43:20</t>
+          <t>2026-05-18 10:53:30</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:21:58</t>
+          <t>2026-05-20 17:13:40</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>谢蜀岷</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:14:24</t>
+          <t>2026-05-18 15:08:39</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>bydesign</t>
+          <t>fixed</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1957,14 +1957,14 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:21:58</t>
+          <t>2026-05-20 17:13:40</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>关于空间清理扫描没有设置超时的问题</t>
+          <t>关于win7环境下，通过Clean调ECG无法跳转指定页面和无法自动扫描的问题</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2009,45 +2009,45 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13 17:03:58</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>邓贵星</t>
-        </is>
-      </c>
+          <t>2026-05-18 09:46:35</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18 10:16:03</t>
+          <t>2026-05-20 09:57:26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>贺照云</t>
+          <t>余悦</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 17:18:10</t>
+          <t>2026-05-18 14:17:57</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>willnotfix</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 09:57:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>42409</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>活动入口</t>
+          <t>空间管理</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>关于hover 图片异常时也能进行入口显示问题</t>
+          <t>关于Clean-空间分析Folder部分内容显示异常的问题</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2082,55 +2082,55 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>辜健</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 14:02:34</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>贺照云</t>
-        </is>
-      </c>
+          <t>2026-05-15 10:10:27</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 16:28:19</t>
+          <t>2026-05-20 09:35:10</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>韦家鹏</t>
+          <t>谢蜀岷</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 16:27:46</t>
+          <t>2026-05-18 13:02:20</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>nonproblem</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>何峻</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0000-00-00 00:00:00</t>
+          <t>2026-05-20 09:35:10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>42469</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>关于ecg本地和自带的数据扫描出来不一致问题</t>
+          <t>关于Space Analyze 进度显示问题</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2175,28 +2175,28 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 11:13:48</t>
+          <t>2026-05-15 10:43:20</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:20</t>
+          <t>2026-05-19 17:21:58</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>谢蜀岷</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 14:22:07</t>
+          <t>2026-05-18 10:14:24</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>bydesign</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2206,14 +2206,14 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19 17:22:20</t>
+          <t>2026-05-19 17:21:58</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>点击scan调用ecg后，经常出现任务栏图标显示不出来的现象</t>
+          <t>关于空间清理扫描没有设置超时的问题</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2253,43 +2253,209 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>何峻</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09 14:54:25</t>
+          <t>2026-05-13 17:03:58</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>刘冬</t>
+          <t>邓贵星</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 09:35:23</t>
+          <t>2026-05-18 10:16:03</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>余悦</t>
+          <t>贺照云</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15 09:30:45</t>
+          <t>2026-05-15 17:18:10</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>willnotfix</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>42409</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>活动入口</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>关于hover 图片异常时也能进行入口显示问题</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>resolved</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:34</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>贺照云</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:28:19</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>韦家鹏</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 16:27:46</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>nonproblem</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0000-00-00 00:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>42471</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5.0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>EPM20.5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>关于ecg本地和自带的数据扫描出来不一致问题</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 11:13:48</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:20</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>余悦</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:22:07</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>辜健</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 17:22:20</t>
         </is>
       </c>
     </row>
